--- a/HMS_Data_Base.xlsx
+++ b/HMS_Data_Base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\me\VIIIth sem project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F7E7FB2-DD76-4CDA-9875-6EE0EF999411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D24FE83E-9460-45CB-A992-2EB38C116EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{2ED1275A-D99F-4A08-8308-2AC67240EDC4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{2ED1275A-D99F-4A08-8308-2AC67240EDC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Patient" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Receptionist" sheetId="4" r:id="rId4"/>
     <sheet name="Lab Technician" sheetId="5" r:id="rId5"/>
     <sheet name="Pharmacist" sheetId="6" r:id="rId6"/>
+    <sheet name="assign care order" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1752" uniqueCount="769">
   <si>
     <t>Patient ID</t>
   </si>
@@ -1934,6 +1935,420 @@
   </si>
   <si>
     <t>prakash.pharma@gmail.com</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>last_visit</t>
+  </si>
+  <si>
+    <t>medical_condition</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>blood_type</t>
+  </si>
+  <si>
+    <t>allergies</t>
+  </si>
+  <si>
+    <t>Diabetes</t>
+  </si>
+  <si>
+    <t>Outpatient</t>
+  </si>
+  <si>
+    <t>O+</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>B+</t>
+  </si>
+  <si>
+    <t>Dust</t>
+  </si>
+  <si>
+    <t>Hypertension</t>
+  </si>
+  <si>
+    <t>A+</t>
+  </si>
+  <si>
+    <t>Heart Disease</t>
+  </si>
+  <si>
+    <t>Inpatient</t>
+  </si>
+  <si>
+    <t>O-</t>
+  </si>
+  <si>
+    <t>Penicillin</t>
+  </si>
+  <si>
+    <t>Migraine</t>
+  </si>
+  <si>
+    <t>AB+</t>
+  </si>
+  <si>
+    <t>Viral Fever</t>
+  </si>
+  <si>
+    <t>B-</t>
+  </si>
+  <si>
+    <t>Gastritis</t>
+  </si>
+  <si>
+    <t>Spicy Food</t>
+  </si>
+  <si>
+    <t>Asthma</t>
+  </si>
+  <si>
+    <t>Arthritis</t>
+  </si>
+  <si>
+    <t>Cold</t>
+  </si>
+  <si>
+    <t>Cardiac Issue</t>
+  </si>
+  <si>
+    <t>A-</t>
+  </si>
+  <si>
+    <t>Sugar</t>
+  </si>
+  <si>
+    <t>Pregnancy</t>
+  </si>
+  <si>
+    <t>Thyroid</t>
+  </si>
+  <si>
+    <t>Allergy</t>
+  </si>
+  <si>
+    <t>Peanuts</t>
+  </si>
+  <si>
+    <t>bp</t>
+  </si>
+  <si>
+    <t>heart_rate</t>
+  </si>
+  <si>
+    <t>temperature</t>
+  </si>
+  <si>
+    <t>spo2</t>
+  </si>
+  <si>
+    <t>128/84</t>
+  </si>
+  <si>
+    <t>110/70</t>
+  </si>
+  <si>
+    <t>145/95</t>
+  </si>
+  <si>
+    <t>120/80</t>
+  </si>
+  <si>
+    <t>118/78</t>
+  </si>
+  <si>
+    <t>125/82</t>
+  </si>
+  <si>
+    <t>130/85</t>
+  </si>
+  <si>
+    <t>135/88</t>
+  </si>
+  <si>
+    <t>118/76</t>
+  </si>
+  <si>
+    <t>140/90</t>
+  </si>
+  <si>
+    <t>122/80</t>
+  </si>
+  <si>
+    <t>138/92</t>
+  </si>
+  <si>
+    <t>115/72</t>
+  </si>
+  <si>
+    <t>132/86</t>
+  </si>
+  <si>
+    <t>118/75</t>
+  </si>
+  <si>
+    <t>140/88</t>
+  </si>
+  <si>
+    <t>125/83</t>
+  </si>
+  <si>
+    <t>112/70</t>
+  </si>
+  <si>
+    <t>118/74</t>
+  </si>
+  <si>
+    <t>135/86</t>
+  </si>
+  <si>
+    <t>120/78</t>
+  </si>
+  <si>
+    <t>116/72</t>
+  </si>
+  <si>
+    <t>125/80</t>
+  </si>
+  <si>
+    <t>138/90</t>
+  </si>
+  <si>
+    <t>130/84</t>
+  </si>
+  <si>
+    <t>130/86</t>
+  </si>
+  <si>
+    <t>140/92</t>
+  </si>
+  <si>
+    <t>135/85</t>
+  </si>
+  <si>
+    <t>132/84</t>
+  </si>
+  <si>
+    <t>120/76</t>
+  </si>
+  <si>
+    <t>128/82</t>
+  </si>
+  <si>
+    <t>138/88</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>patient_id</t>
+  </si>
+  <si>
+    <t>patient_name</t>
+  </si>
+  <si>
+    <t>order_type</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>instruction</t>
+  </si>
+  <si>
+    <t>Medication</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Administer Metformin 500 mg orally twice daily after meals and monitor blood sugar levels.</t>
+  </si>
+  <si>
+    <t>Observation</t>
+  </si>
+  <si>
+    <t>Check patient temperature and respiratory rate every 4 hours for fever monitoring.</t>
+  </si>
+  <si>
+    <t>Procedure</t>
+  </si>
+  <si>
+    <t>Urgent</t>
+  </si>
+  <si>
+    <t>Prepare patient for ECG test and assist cardiologist during procedure.</t>
+  </si>
+  <si>
+    <t>Administer antihypertensive medication and monitor blood pressure every 2 hours.</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>Provide low sodium diet and ensure adequate fluid intake.</t>
+  </si>
+  <si>
+    <t>Observe patient for signs of dehydration and record vitals every 6 hours.</t>
+  </si>
+  <si>
+    <t>Give antacid medication before meals for gastritis treatment.</t>
+  </si>
+  <si>
+    <t>Check blood glucose levels before breakfast and dinner daily.</t>
+  </si>
+  <si>
+    <t>Assist doctor with nebulization therapy for asthma symptoms.</t>
+  </si>
+  <si>
+    <t>Mobility</t>
+  </si>
+  <si>
+    <t>Assist patient with walking exercise for 10 minutes twice daily.</t>
+  </si>
+  <si>
+    <t>Monitor temperature and oxygen saturation every 6 hours.</t>
+  </si>
+  <si>
+    <t>Prepare patient for cardiac stress test and monitor vital signs continuously.</t>
+  </si>
+  <si>
+    <t>Administer paracetamol 500 mg every 6 hours for fever.</t>
+  </si>
+  <si>
+    <t>Check blood pressure every 4 hours due to hypertension history.</t>
+  </si>
+  <si>
+    <t>Administer migraine medication and observe for side effects.</t>
+  </si>
+  <si>
+    <t>Ensure diabetic diet plan with controlled carbohydrate intake.</t>
+  </si>
+  <si>
+    <t>Monitor patient symptoms related to cold and record vitals.</t>
+  </si>
+  <si>
+    <t>Administer inhaler therapy for asthma under doctor supervision.</t>
+  </si>
+  <si>
+    <t>Administer antiviral medication for viral fever treatment.</t>
+  </si>
+  <si>
+    <t>Provide low acid diet to reduce gastritis symptoms.</t>
+  </si>
+  <si>
+    <t>Monitor blood pressure and fetal movement during pregnancy checkup.</t>
+  </si>
+  <si>
+    <t>Administer thyroid medication once daily before breakfast.</t>
+  </si>
+  <si>
+    <t>Ensure diabetic diet and monitor blood sugar levels before meals.</t>
+  </si>
+  <si>
+    <t>Administer migraine pain relief medication as prescribed.</t>
+  </si>
+  <si>
+    <t>Check temperature every 4 hours for fever monitoring.</t>
+  </si>
+  <si>
+    <t>Observe patient for cold symptoms and record respiratory rate.</t>
+  </si>
+  <si>
+    <t>Assist with inhalation therapy for asthma treatment.</t>
+  </si>
+  <si>
+    <t>Administer antihistamine medication for allergy symptoms.</t>
+  </si>
+  <si>
+    <t>Monitor blood pressure twice daily for hypertension control.</t>
+  </si>
+  <si>
+    <t>Provide diabetic meal plan and monitor glucose levels.</t>
+  </si>
+  <si>
+    <t>Monitor temperature and pulse every 6 hours.</t>
+  </si>
+  <si>
+    <t>Administer antipyretic medication for fever relief.</t>
+  </si>
+  <si>
+    <t>Assist doctor with breathing therapy session.</t>
+  </si>
+  <si>
+    <t>Administer migraine medication and observe patient response.</t>
+  </si>
+  <si>
+    <t>Monitor thyroid patient for fatigue and weight changes.</t>
+  </si>
+  <si>
+    <t>Ensure controlled sugar intake for diabetes management.</t>
+  </si>
+  <si>
+    <t>Monitor fever symptoms and record temperature every 4 hours.</t>
+  </si>
+  <si>
+    <t>Administer blood pressure medication daily at scheduled time.</t>
+  </si>
+  <si>
+    <t>Assist patient with physiotherapy exercises twice daily.</t>
+  </si>
+  <si>
+    <t>Check vital signs every 6 hours for cold symptoms.</t>
+  </si>
+  <si>
+    <t>Administer insulin injection before meals as prescribed.</t>
+  </si>
+  <si>
+    <t>Monitor blood pressure every 4 hours.</t>
+  </si>
+  <si>
+    <t>Administer migraine medication if pain level exceeds threshold.</t>
+  </si>
+  <si>
+    <t>Assist doctor with respiratory therapy session.</t>
+  </si>
+  <si>
+    <t>Check temperature and pulse every 6 hours.</t>
+  </si>
+  <si>
+    <t>Administer fever medication and ensure hydration.</t>
+  </si>
+  <si>
+    <t>Monitor blood pressure and oxygen saturation.</t>
+  </si>
+  <si>
+    <t>Provide diet plan avoiding spicy food due to gastritis.</t>
+  </si>
+  <si>
+    <t>Administer migraine medication and observe symptoms.</t>
+  </si>
+  <si>
+    <t>Monitor thyroid condition and check vitals every 8 hours.</t>
   </si>
 </sst>
 </file>
@@ -2021,7 +2436,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2061,6 +2476,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2397,1227 +2827,5175 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF71C010-B571-412F-BF73-9CB1E39E8E5A}">
-  <dimension ref="A2:C102"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="13"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="E1" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="E2" s="12">
+        <v>42</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G2" s="9">
+        <v>9976543001</v>
+      </c>
+      <c r="H2" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="N2" s="9">
+        <v>76</v>
+      </c>
+      <c r="O2" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P2" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="E3" s="12">
+        <v>35</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G3" s="9">
+        <v>9976543002</v>
+      </c>
+      <c r="H3" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="N3" s="9">
+        <v>82</v>
+      </c>
+      <c r="O3" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P3" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="E4" s="12">
+        <v>50</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G4" s="9">
+        <v>9976543003</v>
+      </c>
+      <c r="H4" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="N4" s="9">
+        <v>91</v>
+      </c>
+      <c r="O4" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P4" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="E5" s="12">
+        <v>61</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G5" s="9">
+        <v>9976543004</v>
+      </c>
+      <c r="H5" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="N5" s="9">
+        <v>75</v>
+      </c>
+      <c r="O5" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P5" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="E6" s="12">
+        <v>39</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G6" s="9">
+        <v>9976543005</v>
+      </c>
+      <c r="H6" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="N6" s="9">
+        <v>72</v>
+      </c>
+      <c r="O6" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P6" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="E7" s="12">
+        <v>29</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G7" s="9">
+        <v>9976543006</v>
+      </c>
+      <c r="H7" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="N7" s="9">
+        <v>80</v>
+      </c>
+      <c r="O7" s="9">
+        <v>98.9</v>
+      </c>
+      <c r="P7" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="E8" s="12">
+        <v>31</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G8" s="9">
+        <v>9976543007</v>
+      </c>
+      <c r="H8" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="N8" s="9">
+        <v>78</v>
+      </c>
+      <c r="O8" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P8" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="E9" s="12">
+        <v>44</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G9" s="9">
+        <v>9976543008</v>
+      </c>
+      <c r="H9" s="15">
+        <v>45219</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="N9" s="9">
+        <v>83</v>
+      </c>
+      <c r="O9" s="9">
+        <v>99</v>
+      </c>
+      <c r="P9" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="E10" s="12">
+        <v>36</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G10" s="9">
+        <v>9976543009</v>
+      </c>
+      <c r="H10" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N10" s="9">
+        <v>74</v>
+      </c>
+      <c r="O10" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P10" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
+      <c r="E11" s="12">
+        <v>55</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G11" s="9">
+        <v>9976543010</v>
+      </c>
+      <c r="H11" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K11" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="N11" s="9">
+        <v>90</v>
+      </c>
+      <c r="O11" s="9">
+        <v>99.2</v>
+      </c>
+      <c r="P11" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="E12" s="12">
+        <v>27</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G12" s="9">
+        <v>9976543011</v>
+      </c>
+      <c r="H12" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="N12" s="9">
+        <v>77</v>
+      </c>
+      <c r="O12" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P12" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="9">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="E13" s="12">
+        <v>63</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G13" s="9">
+        <v>9976543012</v>
+      </c>
+      <c r="H13" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="N13" s="9">
+        <v>88</v>
+      </c>
+      <c r="O13" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P13" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="9">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
+      <c r="E14" s="12">
+        <v>30</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G14" s="9">
+        <v>9976543013</v>
+      </c>
+      <c r="H14" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N14" s="9">
+        <v>70</v>
+      </c>
+      <c r="O14" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P14" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="9">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="E15" s="12">
+        <v>46</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G15" s="9">
+        <v>9976543014</v>
+      </c>
+      <c r="H15" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K15" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="N15" s="9">
+        <v>82</v>
+      </c>
+      <c r="O15" s="9">
+        <v>98.8</v>
+      </c>
+      <c r="P15" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="E16" s="12">
+        <v>34</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G16" s="9">
+        <v>9976543015</v>
+      </c>
+      <c r="H16" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N16" s="9">
+        <v>74</v>
+      </c>
+      <c r="O16" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P16" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="9">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
+      <c r="E17" s="12">
+        <v>48</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G17" s="9">
+        <v>9976543016</v>
+      </c>
+      <c r="H17" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K17" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="N17" s="9">
+        <v>85</v>
+      </c>
+      <c r="O17" s="9">
+        <v>99</v>
+      </c>
+      <c r="P17" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
+        <v>17</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="E18" s="12">
+        <v>26</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G18" s="9">
+        <v>9976543017</v>
+      </c>
+      <c r="H18" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K18" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="N18" s="9">
+        <v>72</v>
+      </c>
+      <c r="O18" s="9">
+        <v>98.2</v>
+      </c>
+      <c r="P18" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A19" s="9">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
+      <c r="E19" s="12">
+        <v>37</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G19" s="9">
+        <v>9976543018</v>
+      </c>
+      <c r="H19" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K19" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="N19" s="9">
+        <v>78</v>
+      </c>
+      <c r="O19" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P19" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
+      <c r="E20" s="12">
+        <v>28</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G20" s="9">
+        <v>9976543019</v>
+      </c>
+      <c r="H20" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K20" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="N20" s="9">
+        <v>81</v>
+      </c>
+      <c r="O20" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P20" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="E21" s="12">
+        <v>33</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G21" s="9">
+        <v>9976543020</v>
+      </c>
+      <c r="H21" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K21" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N21" s="9">
+        <v>75</v>
+      </c>
+      <c r="O21" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P21" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="E22" s="12">
+        <v>29</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G22" s="9">
+        <v>9976543021</v>
+      </c>
+      <c r="H22" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="N22" s="9">
+        <v>74</v>
+      </c>
+      <c r="O22" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P22" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="E23" s="12">
+        <v>32</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G23" s="9">
+        <v>9976543022</v>
+      </c>
+      <c r="H23" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N23" s="9">
+        <v>76</v>
+      </c>
+      <c r="O23" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P23" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="E24" s="12">
+        <v>40</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G24" s="9">
+        <v>9976543023</v>
+      </c>
+      <c r="H24" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K24" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M24" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="N24" s="9">
+        <v>82</v>
+      </c>
+      <c r="O24" s="9">
+        <v>98.9</v>
+      </c>
+      <c r="P24" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D25" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
+      <c r="E25" s="12">
+        <v>37</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G25" s="9">
+        <v>9976543024</v>
+      </c>
+      <c r="H25" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I25" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N25" s="9">
         <v>75</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="O25" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P25" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="E26" s="12">
+        <v>31</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G26" s="9">
+        <v>9976543025</v>
+      </c>
+      <c r="H26" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K26" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="N26" s="9">
+        <v>72</v>
+      </c>
+      <c r="O26" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P26" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A27" s="9">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
+      <c r="E27" s="12">
+        <v>28</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G27" s="9">
+        <v>9976543026</v>
+      </c>
+      <c r="H27" s="15">
+        <v>45219</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K27" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N27" s="9">
+        <v>74</v>
+      </c>
+      <c r="O27" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P27" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A28" s="9">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D28" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
+      <c r="E28" s="12">
+        <v>34</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G28" s="9">
+        <v>9976543027</v>
+      </c>
+      <c r="H28" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K28" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N28" s="9">
+        <v>80</v>
+      </c>
+      <c r="O28" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P28" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A29" s="9">
+        <v>28</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
+      <c r="E29" s="12">
+        <v>22</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G29" s="9">
+        <v>9976543028</v>
+      </c>
+      <c r="H29" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="N29" s="9">
+        <v>76</v>
+      </c>
+      <c r="O29" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P29" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A30" s="9">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="D30" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
+      <c r="E30" s="12">
+        <v>36</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G30" s="9">
+        <v>9976543029</v>
+      </c>
+      <c r="H30" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="N30" s="9">
+        <v>82</v>
+      </c>
+      <c r="O30" s="9">
+        <v>98.8</v>
+      </c>
+      <c r="P30" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A31" s="9">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="D31" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
+      <c r="E31" s="12">
+        <v>41</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G31" s="9">
+        <v>9976543030</v>
+      </c>
+      <c r="H31" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I31" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K31" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="N31" s="9">
+        <v>88</v>
+      </c>
+      <c r="O31" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P31" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A32" s="9">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D32" s="4" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
+      <c r="E32" s="12">
+        <v>25</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G32" s="9">
+        <v>9976543031</v>
+      </c>
+      <c r="H32" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K32" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N32" s="9">
+        <v>72</v>
+      </c>
+      <c r="O32" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P32" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A33" s="9">
+        <v>32</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
+      <c r="E33" s="12">
+        <v>33</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G33" s="9">
+        <v>9976543032</v>
+      </c>
+      <c r="H33" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N33" s="9">
+        <v>74</v>
+      </c>
+      <c r="O33" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P33" s="9">
         <v>99</v>
       </c>
-      <c r="B35" s="3" t="s">
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A34" s="9">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
+      <c r="E34" s="12">
+        <v>29</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G34" s="9">
+        <v>9976543033</v>
+      </c>
+      <c r="H34" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K34" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="N34" s="9">
+        <v>80</v>
+      </c>
+      <c r="O34" s="9">
+        <v>98.8</v>
+      </c>
+      <c r="P34" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A35" s="9">
+        <v>34</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
+      <c r="E35" s="12">
+        <v>27</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G35" s="9">
+        <v>9976543034</v>
+      </c>
+      <c r="H35" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I35" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N35" s="9">
+        <v>76</v>
+      </c>
+      <c r="O35" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P35" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A36" s="9">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
+      <c r="E36" s="12">
+        <v>38</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G36" s="9">
+        <v>9976543035</v>
+      </c>
+      <c r="H36" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I36" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K36" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M36" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="N36" s="9">
+        <v>77</v>
+      </c>
+      <c r="O36" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P36" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A37" s="9">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="D37" s="4" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
+      <c r="E37" s="12">
+        <v>42</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G37" s="9">
+        <v>9976543036</v>
+      </c>
+      <c r="H37" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I37" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="N37" s="9">
+        <v>83</v>
+      </c>
+      <c r="O37" s="9">
+        <v>99</v>
+      </c>
+      <c r="P37" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A38" s="9">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="D38" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
+      <c r="E38" s="12">
+        <v>35</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G38" s="9">
+        <v>9976543037</v>
+      </c>
+      <c r="H38" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K38" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L38" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M38" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N38" s="9">
+        <v>74</v>
+      </c>
+      <c r="O38" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P38" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A39" s="9">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
+      <c r="E39" s="12">
+        <v>46</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G39" s="9">
+        <v>9976543038</v>
+      </c>
+      <c r="H39" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="N39" s="9">
+        <v>82</v>
+      </c>
+      <c r="O39" s="9">
+        <v>98.8</v>
+      </c>
+      <c r="P39" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A40" s="9">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
+      <c r="E40" s="12">
+        <v>50</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G40" s="9">
+        <v>9976543039</v>
+      </c>
+      <c r="H40" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K40" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L40" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M40" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="N40" s="9">
+        <v>90</v>
+      </c>
+      <c r="O40" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P40" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A41" s="9">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
+      <c r="E41" s="12">
+        <v>21</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G41" s="9">
+        <v>9976543040</v>
+      </c>
+      <c r="H41" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K41" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L41" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M41" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="N41" s="9">
+        <v>72</v>
+      </c>
+      <c r="O41" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P41" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="9">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="D42" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
+      <c r="E42" s="12">
+        <v>45</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G42" s="9">
+        <v>9976543041</v>
+      </c>
+      <c r="H42" s="15">
+        <v>45219</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K42" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L42" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M42" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="N42" s="9">
+        <v>82</v>
+      </c>
+      <c r="O42" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P42" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A43" s="9">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
+      <c r="E43" s="12">
+        <v>54</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G43" s="9">
+        <v>9976543042</v>
+      </c>
+      <c r="H43" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L43" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M43" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="N43" s="9">
+        <v>88</v>
+      </c>
+      <c r="O43" s="9">
+        <v>99</v>
+      </c>
+      <c r="P43" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A44" s="9">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="D44" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
+      <c r="E44" s="12">
+        <v>38</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G44" s="9">
+        <v>9976543043</v>
+      </c>
+      <c r="H44" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K44" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L44" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M44" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N44" s="9">
+        <v>75</v>
+      </c>
+      <c r="O44" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P44" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A45" s="9">
+        <v>44</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="D45" s="4" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
+      <c r="E45" s="12">
+        <v>44</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G45" s="9">
+        <v>9976543044</v>
+      </c>
+      <c r="H45" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N45" s="9">
+        <v>78</v>
+      </c>
+      <c r="O45" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P45" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A46" s="9">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="D46" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
+      <c r="E46" s="12">
+        <v>31</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G46" s="9">
+        <v>9976543045</v>
+      </c>
+      <c r="H46" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K46" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M46" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N46" s="9">
+        <v>74</v>
+      </c>
+      <c r="O46" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P46" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="9">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="D47" s="4" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
+      <c r="E47" s="12">
+        <v>29</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G47" s="9">
+        <v>9976543046</v>
+      </c>
+      <c r="H47" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K47" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L47" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M47" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N47" s="9">
+        <v>76</v>
+      </c>
+      <c r="O47" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P47" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A48" s="9">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="D48" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
+      <c r="E48" s="12">
+        <v>36</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G48" s="9">
+        <v>9976543047</v>
+      </c>
+      <c r="H48" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>664</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="N48" s="9">
+        <v>82</v>
+      </c>
+      <c r="O48" s="9">
+        <v>98.8</v>
+      </c>
+      <c r="P48" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A49" s="9">
+        <v>48</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
+      <c r="E49" s="12">
+        <v>33</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G49" s="9">
+        <v>9976543048</v>
+      </c>
+      <c r="H49" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K49" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N49" s="9">
+        <v>79</v>
+      </c>
+      <c r="O49" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P49" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A50" s="9">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="D50" s="4" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
+      <c r="E50" s="12">
+        <v>30</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G50" s="9">
+        <v>9976543049</v>
+      </c>
+      <c r="H50" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N50" s="9">
+        <v>75</v>
+      </c>
+      <c r="O50" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P50" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A51" s="9">
+        <v>50</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
+      <c r="E51" s="12">
+        <v>34</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G51" s="9">
+        <v>9976543050</v>
+      </c>
+      <c r="H51" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K51" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L51" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M51" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="N51" s="9">
+        <v>77</v>
+      </c>
+      <c r="O51" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P51" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A52" s="9">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
+      <c r="E52" s="12">
+        <v>26</v>
+      </c>
+      <c r="F52" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G52" s="9">
+        <v>9976543051</v>
+      </c>
+      <c r="H52" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K52" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L52" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M52" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N52" s="9">
+        <v>72</v>
+      </c>
+      <c r="O52" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P52" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A53" s="9">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="D53" s="4" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+      <c r="E53" s="12">
+        <v>24</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G53" s="9">
+        <v>9976543052</v>
+      </c>
+      <c r="H53" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="N53" s="9">
+        <v>75</v>
+      </c>
+      <c r="O53" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P53" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="9">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D54" s="4" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
+      <c r="E54" s="12">
+        <v>27</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G54" s="9">
+        <v>9976543053</v>
+      </c>
+      <c r="H54" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J54" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K54" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L54" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M54" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N54" s="9">
+        <v>76</v>
+      </c>
+      <c r="O54" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P54" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A55" s="9">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
+      <c r="E55" s="12">
+        <v>40</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G55" s="9">
+        <v>9976543054</v>
+      </c>
+      <c r="H55" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I55" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J55" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="N55" s="9">
+        <v>84</v>
+      </c>
+      <c r="O55" s="9">
+        <v>99</v>
+      </c>
+      <c r="P55" s="9">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="9">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
+      <c r="E56" s="12">
+        <v>45</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G56" s="9">
+        <v>9976543055</v>
+      </c>
+      <c r="H56" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="N56" s="9">
+        <v>88</v>
+      </c>
+      <c r="O56" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P56" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A57" s="9">
+        <v>56</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="D57" s="4" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
+      <c r="E57" s="12">
+        <v>39</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G57" s="9">
+        <v>9976543056</v>
+      </c>
+      <c r="H57" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K57" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L57" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M57" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="N57" s="9">
+        <v>80</v>
+      </c>
+      <c r="O57" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P57" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="9">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
+      <c r="E58" s="12">
+        <v>37</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G58" s="9">
+        <v>9976543057</v>
+      </c>
+      <c r="H58" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N58" s="9">
+        <v>75</v>
+      </c>
+      <c r="O58" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P58" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A59" s="9">
+        <v>58</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="D59" s="4" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
+      <c r="E59" s="12">
+        <v>41</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G59" s="9">
+        <v>9976543058</v>
+      </c>
+      <c r="H59" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I59" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K59" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L59" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M59" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N59" s="9">
+        <v>78</v>
+      </c>
+      <c r="O59" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P59" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A60" s="9">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D60" s="4" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+      <c r="E60" s="12">
+        <v>35</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G60" s="9">
+        <v>9976543059</v>
+      </c>
+      <c r="H60" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L60" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M60" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N60" s="9">
+        <v>76</v>
+      </c>
+      <c r="O60" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P60" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A61" s="9">
+        <v>60</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="D61" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
+      <c r="E61" s="12">
+        <v>28</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G61" s="9">
+        <v>9976543060</v>
+      </c>
+      <c r="H61" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J61" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K61" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L61" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M61" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N61" s="9">
+        <v>74</v>
+      </c>
+      <c r="O61" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P61" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A62" s="9">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="D62" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
+      <c r="E62" s="12">
+        <v>23</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G62" s="9">
+        <v>9976543061</v>
+      </c>
+      <c r="H62" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I62" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K62" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L62" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M62" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N62" s="9">
+        <v>72</v>
+      </c>
+      <c r="O62" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P62" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A63" s="9">
+        <v>62</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
+      <c r="E63" s="12">
+        <v>25</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G63" s="9">
+        <v>9976543062</v>
+      </c>
+      <c r="H63" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N63" s="9">
+        <v>75</v>
+      </c>
+      <c r="O63" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P63" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A64" s="9">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D64" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+      <c r="E64" s="12">
+        <v>31</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G64" s="9">
+        <v>9976543063</v>
+      </c>
+      <c r="H64" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K64" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="N64" s="9">
+        <v>80</v>
+      </c>
+      <c r="O64" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P64" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A65" s="9">
+        <v>64</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
+      <c r="E65" s="12">
+        <v>42</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G65" s="9">
+        <v>9976543064</v>
+      </c>
+      <c r="H65" s="15">
+        <v>45219</v>
+      </c>
+      <c r="I65" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="N65" s="9">
+        <v>88</v>
+      </c>
+      <c r="O65" s="9">
+        <v>99</v>
+      </c>
+      <c r="P65" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A66" s="9">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="E66" s="12">
+        <v>47</v>
+      </c>
+      <c r="F66" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G66" s="9">
+        <v>9976543065</v>
+      </c>
+      <c r="H66" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K66" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L66" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="N66" s="9">
+        <v>90</v>
+      </c>
+      <c r="O66" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P66" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A67" s="9">
+        <v>66</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="D67" s="4" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
+      <c r="E67" s="12">
+        <v>50</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G67" s="9">
+        <v>9976543066</v>
+      </c>
+      <c r="H67" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K67" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="N67" s="9">
+        <v>92</v>
+      </c>
+      <c r="O67" s="9">
+        <v>99.2</v>
+      </c>
+      <c r="P67" s="9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A68" s="9">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="D68" s="4" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
+      <c r="E68" s="12">
+        <v>36</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G68" s="9">
+        <v>9976543067</v>
+      </c>
+      <c r="H68" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K68" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="N68" s="9">
+        <v>76</v>
+      </c>
+      <c r="O68" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P68" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A69" s="9">
+        <v>68</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="D69" s="4" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
+      <c r="E69" s="12">
+        <v>33</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G69" s="9">
+        <v>9976543068</v>
+      </c>
+      <c r="H69" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I69" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K69" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N69" s="9">
+        <v>78</v>
+      </c>
+      <c r="O69" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P69" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A70" s="9">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
+      <c r="E70" s="12">
+        <v>29</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G70" s="9">
+        <v>9976543069</v>
+      </c>
+      <c r="H70" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K70" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N70" s="9">
+        <v>74</v>
+      </c>
+      <c r="O70" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P70" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A71" s="9">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="D71" s="4" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
+      <c r="E71" s="12">
+        <v>34</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G71" s="9">
+        <v>9976543070</v>
+      </c>
+      <c r="H71" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I71" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K71" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L71" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M71" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N71" s="9">
+        <v>73</v>
+      </c>
+      <c r="O71" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P71" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A72" s="9">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="D72" s="4" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
+      <c r="E72" s="12">
+        <v>45</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G72" s="9">
+        <v>9976543071</v>
+      </c>
+      <c r="H72" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="N72" s="9">
+        <v>85</v>
+      </c>
+      <c r="O72" s="9">
+        <v>99</v>
+      </c>
+      <c r="P72" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A73" s="9">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="D73" s="4" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
+      <c r="E73" s="12">
+        <v>38</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G73" s="9">
+        <v>9976543072</v>
+      </c>
+      <c r="H73" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="N73" s="9">
+        <v>88</v>
+      </c>
+      <c r="O73" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P73" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A74" s="9">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
+      <c r="E74" s="12">
+        <v>52</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G74" s="9">
+        <v>9976543073</v>
+      </c>
+      <c r="H74" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K74" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L74" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M74" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="N74" s="9">
+        <v>92</v>
+      </c>
+      <c r="O74" s="9">
+        <v>99.2</v>
+      </c>
+      <c r="P74" s="9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A75" s="9">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="D75" s="4" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
+      <c r="E75" s="12">
+        <v>41</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G75" s="9">
+        <v>9976543074</v>
+      </c>
+      <c r="H75" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K75" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L75" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M75" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N75" s="9">
+        <v>75</v>
+      </c>
+      <c r="O75" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P75" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A76" s="9">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="D76" s="4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+      <c r="E76" s="12">
+        <v>36</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G76" s="9">
+        <v>9976543075</v>
+      </c>
+      <c r="H76" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K76" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N76" s="9">
+        <v>73</v>
+      </c>
+      <c r="O76" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P76" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A77" s="9">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="D77" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
+      <c r="E77" s="12">
+        <v>44</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G77" s="9">
+        <v>9976543076</v>
+      </c>
+      <c r="H77" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J77" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K77" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="N77" s="9">
+        <v>88</v>
+      </c>
+      <c r="O77" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P77" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A78" s="9">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="D78" s="4" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
+      <c r="E78" s="12">
+        <v>39</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G78" s="9">
+        <v>9976543077</v>
+      </c>
+      <c r="H78" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K78" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="N78" s="9">
+        <v>90</v>
+      </c>
+      <c r="O78" s="9">
+        <v>99.2</v>
+      </c>
+      <c r="P78" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A79" s="9">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D79" s="4" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
+      <c r="E79" s="12">
+        <v>48</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G79" s="9">
+        <v>9976543078</v>
+      </c>
+      <c r="H79" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>651</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="L79" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="N79" s="9">
+        <v>92</v>
+      </c>
+      <c r="O79" s="9">
+        <v>99.3</v>
+      </c>
+      <c r="P79" s="9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A80" s="9">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="D80" s="4" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
+      <c r="E80" s="12">
+        <v>30</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G80" s="9">
+        <v>9976543079</v>
+      </c>
+      <c r="H80" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K80" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L80" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M80" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="N80" s="9">
+        <v>74</v>
+      </c>
+      <c r="O80" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P80" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" s="9">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="D81" s="4" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
+      <c r="E81" s="12">
+        <v>35</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G81" s="9">
+        <v>9976543080</v>
+      </c>
+      <c r="H81" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N81" s="9">
+        <v>76</v>
+      </c>
+      <c r="O81" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P81" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A82" s="9">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D82" s="4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
+      <c r="E82" s="12">
+        <v>40</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G82" s="9">
+        <v>9976543081</v>
+      </c>
+      <c r="H82" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K82" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M82" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N82" s="9">
+        <v>78</v>
+      </c>
+      <c r="O82" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P82" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83" s="9">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="D83" s="4" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
+      <c r="E83" s="12">
+        <v>34</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G83" s="9">
+        <v>9976543082</v>
+      </c>
+      <c r="H83" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K83" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N83" s="9">
+        <v>75</v>
+      </c>
+      <c r="O83" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P83" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A84" s="9">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="D84" s="4" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
+      <c r="E84" s="12">
+        <v>29</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G84" s="9">
+        <v>9976543083</v>
+      </c>
+      <c r="H84" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K84" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M84" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="N84" s="9">
+        <v>72</v>
+      </c>
+      <c r="O84" s="9">
+        <v>98.3</v>
+      </c>
+      <c r="P84" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A85" s="9">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D85" s="4" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+      <c r="E85" s="12">
+        <v>31</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G85" s="9">
+        <v>9976543084</v>
+      </c>
+      <c r="H85" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K85" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L85" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M85" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N85" s="9">
+        <v>74</v>
+      </c>
+      <c r="O85" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P85" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A86" s="9">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="D86" s="4" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
+      <c r="E86" s="12">
+        <v>36</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G86" s="9">
+        <v>9976543085</v>
+      </c>
+      <c r="H86" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K86" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L86" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="M86" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N86" s="9">
+        <v>78</v>
+      </c>
+      <c r="O86" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P86" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A87" s="9">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="D87" s="4" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
+      <c r="E87" s="12">
+        <v>43</v>
+      </c>
+      <c r="F87" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G87" s="9">
+        <v>9976543086</v>
+      </c>
+      <c r="H87" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K87" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L87" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M87" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="N87" s="9">
+        <v>85</v>
+      </c>
+      <c r="O87" s="9">
+        <v>99</v>
+      </c>
+      <c r="P87" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A88" s="9">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="D88" s="4" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
+      <c r="E88" s="12">
+        <v>47</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G88" s="9">
+        <v>9976543087</v>
+      </c>
+      <c r="H88" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K88" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L88" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M88" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="N88" s="9">
+        <v>88</v>
+      </c>
+      <c r="O88" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="P88" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A89" s="9">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="D89" s="4" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
+      <c r="E89" s="12">
+        <v>39</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G89" s="9">
+        <v>9976543088</v>
+      </c>
+      <c r="H89" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N89" s="9">
+        <v>76</v>
+      </c>
+      <c r="O89" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P89" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A90" s="9">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="D90" s="4" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
+      <c r="E90" s="12">
+        <v>41</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G90" s="9">
+        <v>9976543089</v>
+      </c>
+      <c r="H90" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K90" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L90" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M90" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N90" s="9">
+        <v>78</v>
+      </c>
+      <c r="O90" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P90" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A91" s="9">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="D91" s="4" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
+      <c r="E91" s="12">
+        <v>33</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G91" s="9">
+        <v>9976543090</v>
+      </c>
+      <c r="H91" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K91" s="9" t="s">
+        <v>655</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M91" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N91" s="9">
+        <v>75</v>
+      </c>
+      <c r="O91" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P91" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A92" s="9">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="D92" s="4" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
+      <c r="E92" s="12">
+        <v>49</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G92" s="9">
+        <v>9976543091</v>
+      </c>
+      <c r="H92" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K92" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L92" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M92" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="N92" s="9">
+        <v>85</v>
+      </c>
+      <c r="O92" s="9">
+        <v>99</v>
+      </c>
+      <c r="P92" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A93" s="9">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="D93" s="4" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
+      <c r="E93" s="12">
+        <v>38</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G93" s="9">
+        <v>9976543092</v>
+      </c>
+      <c r="H93" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="N93" s="9">
+        <v>80</v>
+      </c>
+      <c r="O93" s="9">
+        <v>98.7</v>
+      </c>
+      <c r="P93" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A94" s="9">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="D94" s="4" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
+      <c r="E94" s="12">
+        <v>27</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G94" s="9">
+        <v>9976543093</v>
+      </c>
+      <c r="H94" s="15">
+        <v>45226</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K94" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M94" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N94" s="9">
+        <v>75</v>
+      </c>
+      <c r="O94" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P94" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A95" s="9">
+        <v>94</v>
+      </c>
+      <c r="B95" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="D95" s="4" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
+      <c r="E95" s="12">
+        <v>35</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G95" s="9">
+        <v>9976543094</v>
+      </c>
+      <c r="H95" s="15">
+        <v>45227</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K95" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M95" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="N95" s="9">
+        <v>73</v>
+      </c>
+      <c r="O95" s="9">
+        <v>98.4</v>
+      </c>
+      <c r="P95" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A96" s="9">
+        <v>95</v>
+      </c>
+      <c r="B96" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="D96" s="4" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
+      <c r="E96" s="12">
+        <v>32</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G96" s="9">
+        <v>9976543095</v>
+      </c>
+      <c r="H96" s="15">
+        <v>45220</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K96" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L96" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M96" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="N96" s="9">
+        <v>74</v>
+      </c>
+      <c r="O96" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P96" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A97" s="9">
+        <v>96</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D97" s="4" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
+      <c r="E97" s="12">
+        <v>37</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G97" s="9">
+        <v>9976543096</v>
+      </c>
+      <c r="H97" s="15">
+        <v>45221</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K97" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="N97" s="9">
+        <v>78</v>
+      </c>
+      <c r="O97" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P97" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A98" s="9">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C98" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="D98" s="4" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
+      <c r="E98" s="12">
+        <v>29</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G98" s="9">
+        <v>9976543097</v>
+      </c>
+      <c r="H98" s="15">
+        <v>45222</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K98" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L98" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="M98" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N98" s="9">
+        <v>75</v>
+      </c>
+      <c r="O98" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P98" s="9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A99" s="9">
+        <v>98</v>
+      </c>
+      <c r="B99" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C99" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="D99" s="4" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
+      <c r="E99" s="12">
+        <v>34</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G99" s="9">
+        <v>9976543098</v>
+      </c>
+      <c r="H99" s="15">
+        <v>45223</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K99" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="L99" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M99" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="N99" s="9">
+        <v>76</v>
+      </c>
+      <c r="O99" s="9">
+        <v>98.6</v>
+      </c>
+      <c r="P99" s="9">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A100" s="9">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="D100" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
+      <c r="E100" s="12">
+        <v>40</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="G100" s="9">
+        <v>9976543099</v>
+      </c>
+      <c r="H100" s="15">
+        <v>45224</v>
+      </c>
+      <c r="I100" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="J100" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K100" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="L100" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M100" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="N100" s="9">
+        <v>88</v>
+      </c>
+      <c r="O100" s="9">
+        <v>99</v>
+      </c>
+      <c r="P100" s="9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A101" s="9">
+        <v>100</v>
+      </c>
+      <c r="B101" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="C101" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>302</v>
+      </c>
+      <c r="E101" s="12">
+        <v>28</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>634</v>
+      </c>
+      <c r="G101" s="9">
+        <v>9976543100</v>
+      </c>
+      <c r="H101" s="15">
+        <v>45225</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>642</v>
+      </c>
+      <c r="K101" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="L101" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="M101" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="N101" s="9">
+        <v>75</v>
+      </c>
+      <c r="O101" s="9">
+        <v>98.5</v>
+      </c>
+      <c r="P101" s="9">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="mailto:arulkumar@gmail.com" xr:uid="{209B8D63-4BA0-4DBE-8132-DCDD798416E4}"/>
-    <hyperlink ref="C4" r:id="rId2" display="mailto:karthikraj@gmail.com" xr:uid="{377E331A-243C-46B8-A6C9-F640A26C0FB7}"/>
-    <hyperlink ref="C5" r:id="rId3" display="mailto:vigneshkumar@gmail.com" xr:uid="{3584A542-DBA2-405D-A282-899A43D9840A}"/>
-    <hyperlink ref="C6" r:id="rId4" display="mailto:sureshbabu@gmail.com" xr:uid="{50B3222A-42A9-48F4-A007-215421055B2B}"/>
-    <hyperlink ref="C7" r:id="rId5" display="mailto:prakashraj@gmail.com" xr:uid="{9DB706A1-6A90-4E50-9913-B1EA1F4737E9}"/>
-    <hyperlink ref="C8" r:id="rId6" display="mailto:dineshkumar@gmail.com" xr:uid="{637ACCA4-E4E6-413F-B2CF-0AEB40309978}"/>
-    <hyperlink ref="C9" r:id="rId7" display="mailto:gokulraj@gmail.com" xr:uid="{96963548-6DB4-48AD-9B78-56A8ED4D6AD8}"/>
-    <hyperlink ref="C10" r:id="rId8" display="mailto:hariprasad@gmail.com" xr:uid="{4E1FFB0D-9FC7-457A-B302-E1ED50B4B468}"/>
-    <hyperlink ref="C11" r:id="rId9" display="mailto:manojkumar@gmail.com" xr:uid="{8D2F51A4-B922-48D5-BFBD-3513F7203C97}"/>
-    <hyperlink ref="C12" r:id="rId10" display="mailto:saravanan@gmail.com" xr:uid="{381B7CC4-4F81-4CE2-8DA1-F4233628786A}"/>
-    <hyperlink ref="C13" r:id="rId11" display="mailto:naveenkumar@gmail.com" xr:uid="{7CC379D9-8067-4D85-A2BE-EB5861007CC8}"/>
-    <hyperlink ref="C14" r:id="rId12" display="mailto:rameshkumar@gmail.com" xr:uid="{DE09824E-37E9-44BA-BD45-FF2A71C75C35}"/>
-    <hyperlink ref="C15" r:id="rId13" display="mailto:lokeshkumar@gmail.com" xr:uid="{C55BEE44-FAFB-4FAB-A9C1-29B1A30D1D0F}"/>
-    <hyperlink ref="C16" r:id="rId14" display="mailto:balamurugan@gmail.com" xr:uid="{98EB7EB7-EE30-449E-BEB9-5BC422C03F66}"/>
-    <hyperlink ref="C17" r:id="rId15" display="mailto:ashwinkumar@gmail.com" xr:uid="{B614FBEF-9D24-4AE9-B0C8-95C1074CBC40}"/>
-    <hyperlink ref="C18" r:id="rId16" display="mailto:muthukumar@gmail.com" xr:uid="{7F1B723C-2CA6-49D2-B7B6-9F45BC0F650D}"/>
-    <hyperlink ref="C19" r:id="rId17" display="mailto:praveenkumar@gmail.com" xr:uid="{F397254A-4EBD-414B-9945-7662422FF55C}"/>
-    <hyperlink ref="C20" r:id="rId18" display="mailto:sathishkumar@gmail.com" xr:uid="{B376BDCC-CBAC-4340-8F3A-E82E9EAEBE5A}"/>
-    <hyperlink ref="C21" r:id="rId19" display="mailto:tharunkumar@gmail.com" xr:uid="{FF6F611A-03FC-49F9-82A2-79C9F34C9C0B}"/>
-    <hyperlink ref="C22" r:id="rId20" display="mailto:kavinraj@gmail.com" xr:uid="{8778497E-D0C5-4231-A87B-5BF131A8C0CC}"/>
-    <hyperlink ref="C23" r:id="rId21" display="mailto:anitha@gmail.com" xr:uid="{1CF9F06C-211D-41DB-A49C-1657C063E2F1}"/>
-    <hyperlink ref="C24" r:id="rId22" display="mailto:divyalakshmi@gmail.com" xr:uid="{C06D440F-5B2A-4351-8498-2C44B77B784B}"/>
-    <hyperlink ref="C25" r:id="rId23" display="mailto:meena@gmail.com" xr:uid="{6D2DBD6D-9752-4BD7-83DA-A855FC9E0526}"/>
-    <hyperlink ref="C26" r:id="rId24" display="mailto:kavitha@gmail.com" xr:uid="{D4866479-7D28-4D72-B4C7-A5A1440A47B7}"/>
-    <hyperlink ref="C27" r:id="rId25" display="mailto:nandhini@gmail.com" xr:uid="{3C7AF42F-EBF8-41F6-A7C3-9730ED7D12BD}"/>
-    <hyperlink ref="C28" r:id="rId26" display="mailto:priya@gmail.com" xr:uid="{1280683C-B012-415F-BDB5-66C9C1A99436}"/>
-    <hyperlink ref="C29" r:id="rId27" display="mailto:deepika@gmail.com" xr:uid="{BE6A4718-4E9A-40A8-80D8-A612F6230BA1}"/>
-    <hyperlink ref="C30" r:id="rId28" display="mailto:harini@gmail.com" xr:uid="{E03B1A9B-B793-470F-B222-6CF8C0030535}"/>
-    <hyperlink ref="C31" r:id="rId29" display="mailto:swetha@gmail.com" xr:uid="{F4481F2A-32A7-4D9A-B54C-FF0AFB6F6CA9}"/>
-    <hyperlink ref="C32" r:id="rId30" display="mailto:ramya@gmail.com" xr:uid="{054F8856-EC70-495A-9E70-38926BEB50A1}"/>
-    <hyperlink ref="C33" r:id="rId31" display="mailto:keerthana@gmail.com" xr:uid="{E7C40EB8-E88C-4BC4-BE5C-46D8156FFBC7}"/>
-    <hyperlink ref="C34" r:id="rId32" display="mailto:janani@gmail.com" xr:uid="{F97DCA79-CFDD-4F98-996D-6BD5D9FD5F33}"/>
-    <hyperlink ref="C35" r:id="rId33" display="mailto:aishwarya@gmail.com" xr:uid="{591B536A-C719-4826-948B-E615B37E3FD1}"/>
-    <hyperlink ref="C36" r:id="rId34" display="mailto:monisha@gmail.com" xr:uid="{F76FB992-85AC-496F-823C-FAEA6A2AA011}"/>
-    <hyperlink ref="C37" r:id="rId35" display="mailto:pavithra@gmail.com" xr:uid="{125E7E3D-EF27-42DC-B3B4-281EB039EBA1}"/>
-    <hyperlink ref="C38" r:id="rId36" display="mailto:subashini@gmail.com" xr:uid="{FAADE00F-C1D3-4594-985E-1D71EB8E161C}"/>
-    <hyperlink ref="C39" r:id="rId37" display="mailto:gayathri@gmail.com" xr:uid="{934E2D74-7EC2-4E34-9F51-3692A690895F}"/>
-    <hyperlink ref="C40" r:id="rId38" display="mailto:revathi@gmail.com" xr:uid="{396CC2BA-F233-4FAF-8892-39513A76D39C}"/>
-    <hyperlink ref="C41" r:id="rId39" display="mailto:mahalakshmi@gmail.com" xr:uid="{7E11DAF5-E7F9-4A58-BD66-9B5DEA4485D5}"/>
-    <hyperlink ref="C42" r:id="rId40" display="mailto:yazhini@gmail.com" xr:uid="{F6A31C5E-B3AC-49FA-9F06-495F54AF820B}"/>
-    <hyperlink ref="C43" r:id="rId41" display="mailto:aravind@gmail.com" xr:uid="{A05D629B-EB57-4BAF-9FAD-D013C46A89B8}"/>
-    <hyperlink ref="C44" r:id="rId42" display="mailto:senthilkumar@gmail.com" xr:uid="{6CE63AC4-7181-483F-9A2B-DE4DE0438ED0}"/>
-    <hyperlink ref="C45" r:id="rId43" display="mailto:vijaykumar@gmail.com" xr:uid="{C6AA3F15-FE15-43E8-82D9-DACFCFDEABEF}"/>
-    <hyperlink ref="C46" r:id="rId44" display="mailto:ajithkumar@gmail.com" xr:uid="{C65743B2-EFBB-4D86-9945-F4FB25618B21}"/>
-    <hyperlink ref="C47" r:id="rId45" display="mailto:suryaprakash@gmail.com" xr:uid="{8763A978-44DC-4780-A07C-5B439E140C77}"/>
-    <hyperlink ref="C48" r:id="rId46" display="mailto:dhanush@gmail.com" xr:uid="{C289B447-DF1F-41AC-85AB-51634274EFDC}"/>
-    <hyperlink ref="C49" r:id="rId47" display="mailto:vikram@gmail.com" xr:uid="{EB52E18D-7125-4C4F-B19C-0DF9F0EAE07B}"/>
-    <hyperlink ref="C50" r:id="rId48" display="mailto:jeeva@gmail.com" xr:uid="{10B2E870-4813-42F7-98CD-BC7692C1C30C}"/>
-    <hyperlink ref="C51" r:id="rId49" display="mailto:karthika@gmail.com" xr:uid="{3406B273-9E3B-4DAE-8C56-3D52E118633F}"/>
-    <hyperlink ref="C52" r:id="rId50" display="mailto:lakshmipriya@gmail.com" xr:uid="{A83725F0-0FF6-4B77-A80F-DE572F95F1F3}"/>
-    <hyperlink ref="C53" r:id="rId51" display="mailto:nithya@gmail.com" xr:uid="{A3D793AD-12E9-4AD6-A72D-51A0A212B157}"/>
-    <hyperlink ref="C54" r:id="rId52" display="mailto:sanjana@gmail.com" xr:uid="{3DEA9A78-4C09-4D46-ADF5-6F59F3E8D4E6}"/>
-    <hyperlink ref="C55" r:id="rId53" display="mailto:vaishnavi@gmail.com" xr:uid="{E56E5D1D-10F6-48E2-AF72-59178CA91F05}"/>
-    <hyperlink ref="C56" r:id="rId54" display="mailto:hemalatha@gmail.com" xr:uid="{C726BD77-ED9A-40A5-B004-0970FB0FDF08}"/>
-    <hyperlink ref="C57" r:id="rId55" display="mailto:selvi@gmail.com" xr:uid="{751C491A-9FCD-4738-9600-83DA7E64B62A}"/>
-    <hyperlink ref="C58" r:id="rId56" display="mailto:malathi@gmail.com" xr:uid="{1C93E6D3-C401-402A-B53D-1F32B7D2248C}"/>
-    <hyperlink ref="C59" r:id="rId57" display="mailto:chitra@gmail.com" xr:uid="{AE1EFBD4-CDA9-4E79-82CA-06019F13465E}"/>
-    <hyperlink ref="C60" r:id="rId58" display="mailto:umamaheswari@gmail.com" xr:uid="{F43D2525-3BF5-4346-92FE-12AA629CEA8D}"/>
-    <hyperlink ref="C61" r:id="rId59" display="mailto:bharathkumar@gmail.com" xr:uid="{A9859F1B-192F-48FA-94FD-479353A57679}"/>
-    <hyperlink ref="C62" r:id="rId60" display="mailto:naveena@gmail.com" xr:uid="{3FB39B51-DBC6-4D28-AA17-BA8A7E48FE69}"/>
-    <hyperlink ref="C63" r:id="rId61" display="mailto:rithika@gmail.com" xr:uid="{6F347DA5-955E-4123-95F3-3B8851E9F8A3}"/>
-    <hyperlink ref="C64" r:id="rId62" display="mailto:abinaya@gmail.com" xr:uid="{FD5CE39C-69C6-4364-A0CE-E233F531B749}"/>
-    <hyperlink ref="C65" r:id="rId63" display="mailto:gowtham@gmail.com" xr:uid="{2D8C35F9-E1CB-44F2-9606-E4E75129B4B1}"/>
-    <hyperlink ref="C66" r:id="rId64" display="mailto:arunprasad@gmail.com" xr:uid="{BD743DF5-C37D-4650-B344-B600E82B41D6}"/>
-    <hyperlink ref="C67" r:id="rId65" display="mailto:maheshkumar@gmail.com" xr:uid="{3120E2D9-FED1-4C85-A197-56984E24E938}"/>
-    <hyperlink ref="C68" r:id="rId66" display="mailto:rajeshkumar@gmail.com" xr:uid="{79A6109D-B720-4FC9-BB27-E8B881A2B597}"/>
-    <hyperlink ref="C69" r:id="rId67" display="mailto:kamesh@gmail.com" xr:uid="{CB48D24D-E237-4E94-8F9D-23B1F4D80348}"/>
-    <hyperlink ref="C70" r:id="rId68" display="mailto:yogesh@gmail.com" xr:uid="{81C35A21-03DA-4CB5-A430-83ECA5648333}"/>
-    <hyperlink ref="C71" r:id="rId69" display="mailto:santhoshkumar@gmail.com" xr:uid="{4957098F-C270-44E5-8030-7344AA552C8C}"/>
-    <hyperlink ref="C72" r:id="rId70" display="mailto:vasanth@gmail.com" xr:uid="{9689123A-DFF3-44E5-80C8-A4651E839987}"/>
-    <hyperlink ref="C73" r:id="rId71" display="mailto:murali@gmail.com" xr:uid="{5CF7B1FD-EF90-400B-8C94-ADCEC2B11484}"/>
-    <hyperlink ref="C74" r:id="rId72" display="mailto:parthiban@gmail.com" xr:uid="{F4F28E89-5EFB-4369-84B4-9982C6935B73}"/>
-    <hyperlink ref="C75" r:id="rId73" display="mailto:selvaraj@gmail.com" xr:uid="{A80AFDDB-AE1E-497F-BCD9-22D380D9CE4B}"/>
-    <hyperlink ref="C76" r:id="rId74" display="mailto:kumaravel@gmail.com" xr:uid="{6DAE3499-11BB-4620-AAA4-833C85B55B82}"/>
-    <hyperlink ref="C77" r:id="rId75" display="mailto:boopathy@gmail.com" xr:uid="{74C74642-54DC-42AD-9BB1-FA1B43D70A8F}"/>
-    <hyperlink ref="C78" r:id="rId76" display="mailto:thirumal@gmail.com" xr:uid="{B6B9A52F-F8BA-4C58-823E-453428F68D15}"/>
-    <hyperlink ref="C79" r:id="rId77" display="mailto:ilango@gmail.com" xr:uid="{8A3DF50F-4D20-47EA-A0C9-9B624E2E8BA6}"/>
-    <hyperlink ref="C80" r:id="rId78" display="mailto:perumal@gmail.com" xr:uid="{34ED624F-240B-42A8-9F73-BE56929FE4CA}"/>
-    <hyperlink ref="C81" r:id="rId79" display="mailto:malar@gmail.com" xr:uid="{95550360-0FDF-4265-B93B-304E67EC85E0}"/>
-    <hyperlink ref="C82" r:id="rId80" display="mailto:kanimozhi@gmail.com" xr:uid="{498C34F3-6BBC-4503-9188-3FFC8BFA4B7D}"/>
-    <hyperlink ref="C83" r:id="rId81" display="mailto:thenmozhi@gmail.com" xr:uid="{D0029955-563E-4876-9951-5FC32A044282}"/>
-    <hyperlink ref="C84" r:id="rId82" display="mailto:anbarasi@gmail.com" xr:uid="{B59582A9-C347-4820-A362-114296BCBCE5}"/>
-    <hyperlink ref="C85" r:id="rId83" display="mailto:poornima@gmail.com" xr:uid="{248DFAC6-F35B-4806-A757-A33EF05FF5D3}"/>
-    <hyperlink ref="C86" r:id="rId84" display="mailto:suganya@gmail.com" xr:uid="{0BB5B6E6-2855-49D0-9788-9F62C5E9DF2E}"/>
-    <hyperlink ref="C87" r:id="rId85" display="mailto:rohini@gmail.com" xr:uid="{B95119B9-8243-4FA5-AA60-CFB1DA34D438}"/>
-    <hyperlink ref="C88" r:id="rId86" display="mailto:sangeetha@gmail.com" xr:uid="{B5A2B8EB-25E8-4AEF-B535-29D50409346E}"/>
-    <hyperlink ref="C89" r:id="rId87" display="mailto:bhavani@gmail.com" xr:uid="{B933B64E-5A92-482E-A01B-4FEB09544F64}"/>
-    <hyperlink ref="C90" r:id="rId88" display="mailto:kokila@gmail.com" xr:uid="{4ED53F70-AE17-4902-A0F4-88797D99C5DF}"/>
-    <hyperlink ref="C91" r:id="rId89" display="mailto:sridevi@gmail.com" xr:uid="{D48651A8-CF01-403A-979B-B4F66692E009}"/>
-    <hyperlink ref="C92" r:id="rId90" display="mailto:vidhya@gmail.com" xr:uid="{0577CF7C-A955-4472-83EC-277CC26544EA}"/>
-    <hyperlink ref="C93" r:id="rId91" display="mailto:elango@gmail.com" xr:uid="{2F70A94C-8EDD-4210-9C20-CD1BAD891768}"/>
-    <hyperlink ref="C94" r:id="rId92" display="mailto:chandru@gmail.com" xr:uid="{6C272207-254B-4CB7-B867-A4A37FDDCFB5}"/>
-    <hyperlink ref="C95" r:id="rId93" display="mailto:prithvi@gmail.com" xr:uid="{6101FF68-0A71-4F4F-B62E-7884CE25B49E}"/>
-    <hyperlink ref="C96" r:id="rId94" display="mailto:devan@gmail.com" xr:uid="{4E23B004-06D7-4604-9E6F-7E5A658AF5C2}"/>
-    <hyperlink ref="C97" r:id="rId95" display="mailto:kowsalya@gmail.com" xr:uid="{7F0CA384-0CB3-484E-ACA9-7092E94E5DAA}"/>
-    <hyperlink ref="C98" r:id="rId96" display="mailto:renuka@gmail.com" xr:uid="{B5121CD3-56FF-4091-AE3B-C8A2D4B5324A}"/>
-    <hyperlink ref="C99" r:id="rId97" display="mailto:madhumitha@gmail.com" xr:uid="{0427B80F-EB9D-47A3-9298-D46C8D9DAE6F}"/>
-    <hyperlink ref="C100" r:id="rId98" display="mailto:jothika@gmail.com" xr:uid="{6C51BE3E-DB8F-48FE-9D0C-5FEC085EB456}"/>
-    <hyperlink ref="C101" r:id="rId99" display="mailto:thamarai@gmail.com" xr:uid="{B642DC14-C65E-4E03-B531-ADC668A2DE34}"/>
-    <hyperlink ref="C102" r:id="rId100" display="mailto:iniyan@gmail.com" xr:uid="{AFC574C4-2D58-4F27-96F4-12B0290E8E21}"/>
+    <hyperlink ref="D2" r:id="rId1" display="mailto:arulkumar@gmail.com" xr:uid="{209B8D63-4BA0-4DBE-8132-DCDD798416E4}"/>
+    <hyperlink ref="D3" r:id="rId2" display="mailto:karthikraj@gmail.com" xr:uid="{377E331A-243C-46B8-A6C9-F640A26C0FB7}"/>
+    <hyperlink ref="D4" r:id="rId3" display="mailto:vigneshkumar@gmail.com" xr:uid="{3584A542-DBA2-405D-A282-899A43D9840A}"/>
+    <hyperlink ref="D5" r:id="rId4" display="mailto:sureshbabu@gmail.com" xr:uid="{50B3222A-42A9-48F4-A007-215421055B2B}"/>
+    <hyperlink ref="D6" r:id="rId5" display="mailto:prakashraj@gmail.com" xr:uid="{9DB706A1-6A90-4E50-9913-B1EA1F4737E9}"/>
+    <hyperlink ref="D7" r:id="rId6" display="mailto:dineshkumar@gmail.com" xr:uid="{637ACCA4-E4E6-413F-B2CF-0AEB40309978}"/>
+    <hyperlink ref="D8" r:id="rId7" display="mailto:gokulraj@gmail.com" xr:uid="{96963548-6DB4-48AD-9B78-56A8ED4D6AD8}"/>
+    <hyperlink ref="D9" r:id="rId8" display="mailto:hariprasad@gmail.com" xr:uid="{4E1FFB0D-9FC7-457A-B302-E1ED50B4B468}"/>
+    <hyperlink ref="D10" r:id="rId9" display="mailto:manojkumar@gmail.com" xr:uid="{8D2F51A4-B922-48D5-BFBD-3513F7203C97}"/>
+    <hyperlink ref="D11" r:id="rId10" display="mailto:saravanan@gmail.com" xr:uid="{381B7CC4-4F81-4CE2-8DA1-F4233628786A}"/>
+    <hyperlink ref="D12" r:id="rId11" display="mailto:naveenkumar@gmail.com" xr:uid="{7CC379D9-8067-4D85-A2BE-EB5861007CC8}"/>
+    <hyperlink ref="D13" r:id="rId12" display="mailto:rameshkumar@gmail.com" xr:uid="{DE09824E-37E9-44BA-BD45-FF2A71C75C35}"/>
+    <hyperlink ref="D14" r:id="rId13" display="mailto:lokeshkumar@gmail.com" xr:uid="{C55BEE44-FAFB-4FAB-A9C1-29B1A30D1D0F}"/>
+    <hyperlink ref="D15" r:id="rId14" display="mailto:balamurugan@gmail.com" xr:uid="{98EB7EB7-EE30-449E-BEB9-5BC422C03F66}"/>
+    <hyperlink ref="D16" r:id="rId15" display="mailto:ashwinkumar@gmail.com" xr:uid="{B614FBEF-9D24-4AE9-B0C8-95C1074CBC40}"/>
+    <hyperlink ref="D17" r:id="rId16" display="mailto:muthukumar@gmail.com" xr:uid="{7F1B723C-2CA6-49D2-B7B6-9F45BC0F650D}"/>
+    <hyperlink ref="D18" r:id="rId17" display="mailto:praveenkumar@gmail.com" xr:uid="{F397254A-4EBD-414B-9945-7662422FF55C}"/>
+    <hyperlink ref="D19" r:id="rId18" display="mailto:sathishkumar@gmail.com" xr:uid="{B376BDCC-CBAC-4340-8F3A-E82E9EAEBE5A}"/>
+    <hyperlink ref="D20" r:id="rId19" display="mailto:tharunkumar@gmail.com" xr:uid="{FF6F611A-03FC-49F9-82A2-79C9F34C9C0B}"/>
+    <hyperlink ref="D21" r:id="rId20" display="mailto:kavinraj@gmail.com" xr:uid="{8778497E-D0C5-4231-A87B-5BF131A8C0CC}"/>
+    <hyperlink ref="D22" r:id="rId21" display="mailto:anitha@gmail.com" xr:uid="{1CF9F06C-211D-41DB-A49C-1657C063E2F1}"/>
+    <hyperlink ref="D23" r:id="rId22" display="mailto:divyalakshmi@gmail.com" xr:uid="{C06D440F-5B2A-4351-8498-2C44B77B784B}"/>
+    <hyperlink ref="D24" r:id="rId23" display="mailto:meena@gmail.com" xr:uid="{6D2DBD6D-9752-4BD7-83DA-A855FC9E0526}"/>
+    <hyperlink ref="D25" r:id="rId24" display="mailto:kavitha@gmail.com" xr:uid="{D4866479-7D28-4D72-B4C7-A5A1440A47B7}"/>
+    <hyperlink ref="D26" r:id="rId25" display="mailto:nandhini@gmail.com" xr:uid="{3C7AF42F-EBF8-41F6-A7C3-9730ED7D12BD}"/>
+    <hyperlink ref="D27" r:id="rId26" display="mailto:priya@gmail.com" xr:uid="{1280683C-B012-415F-BDB5-66C9C1A99436}"/>
+    <hyperlink ref="D28" r:id="rId27" display="mailto:deepika@gmail.com" xr:uid="{BE6A4718-4E9A-40A8-80D8-A612F6230BA1}"/>
+    <hyperlink ref="D29" r:id="rId28" display="mailto:harini@gmail.com" xr:uid="{E03B1A9B-B793-470F-B222-6CF8C0030535}"/>
+    <hyperlink ref="D30" r:id="rId29" display="mailto:swetha@gmail.com" xr:uid="{F4481F2A-32A7-4D9A-B54C-FF0AFB6F6CA9}"/>
+    <hyperlink ref="D31" r:id="rId30" display="mailto:ramya@gmail.com" xr:uid="{054F8856-EC70-495A-9E70-38926BEB50A1}"/>
+    <hyperlink ref="D32" r:id="rId31" display="mailto:keerthana@gmail.com" xr:uid="{E7C40EB8-E88C-4BC4-BE5C-46D8156FFBC7}"/>
+    <hyperlink ref="D33" r:id="rId32" display="mailto:janani@gmail.com" xr:uid="{F97DCA79-CFDD-4F98-996D-6BD5D9FD5F33}"/>
+    <hyperlink ref="D34" r:id="rId33" display="mailto:aishwarya@gmail.com" xr:uid="{591B536A-C719-4826-948B-E615B37E3FD1}"/>
+    <hyperlink ref="D35" r:id="rId34" display="mailto:monisha@gmail.com" xr:uid="{F76FB992-85AC-496F-823C-FAEA6A2AA011}"/>
+    <hyperlink ref="D36" r:id="rId35" display="mailto:pavithra@gmail.com" xr:uid="{125E7E3D-EF27-42DC-B3B4-281EB039EBA1}"/>
+    <hyperlink ref="D37" r:id="rId36" display="mailto:subashini@gmail.com" xr:uid="{FAADE00F-C1D3-4594-985E-1D71EB8E161C}"/>
+    <hyperlink ref="D38" r:id="rId37" display="mailto:gayathri@gmail.com" xr:uid="{934E2D74-7EC2-4E34-9F51-3692A690895F}"/>
+    <hyperlink ref="D39" r:id="rId38" display="mailto:revathi@gmail.com" xr:uid="{396CC2BA-F233-4FAF-8892-39513A76D39C}"/>
+    <hyperlink ref="D40" r:id="rId39" display="mailto:mahalakshmi@gmail.com" xr:uid="{7E11DAF5-E7F9-4A58-BD66-9B5DEA4485D5}"/>
+    <hyperlink ref="D41" r:id="rId40" display="mailto:yazhini@gmail.com" xr:uid="{F6A31C5E-B3AC-49FA-9F06-495F54AF820B}"/>
+    <hyperlink ref="D42" r:id="rId41" display="mailto:aravind@gmail.com" xr:uid="{A05D629B-EB57-4BAF-9FAD-D013C46A89B8}"/>
+    <hyperlink ref="D43" r:id="rId42" display="mailto:senthilkumar@gmail.com" xr:uid="{6CE63AC4-7181-483F-9A2B-DE4DE0438ED0}"/>
+    <hyperlink ref="D44" r:id="rId43" display="mailto:vijaykumar@gmail.com" xr:uid="{C6AA3F15-FE15-43E8-82D9-DACFCFDEABEF}"/>
+    <hyperlink ref="D45" r:id="rId44" display="mailto:ajithkumar@gmail.com" xr:uid="{C65743B2-EFBB-4D86-9945-F4FB25618B21}"/>
+    <hyperlink ref="D46" r:id="rId45" display="mailto:suryaprakash@gmail.com" xr:uid="{8763A978-44DC-4780-A07C-5B439E140C77}"/>
+    <hyperlink ref="D47" r:id="rId46" display="mailto:dhanush@gmail.com" xr:uid="{C289B447-DF1F-41AC-85AB-51634274EFDC}"/>
+    <hyperlink ref="D48" r:id="rId47" display="mailto:vikram@gmail.com" xr:uid="{EB52E18D-7125-4C4F-B19C-0DF9F0EAE07B}"/>
+    <hyperlink ref="D49" r:id="rId48" display="mailto:jeeva@gmail.com" xr:uid="{10B2E870-4813-42F7-98CD-BC7692C1C30C}"/>
+    <hyperlink ref="D50" r:id="rId49" display="mailto:karthika@gmail.com" xr:uid="{3406B273-9E3B-4DAE-8C56-3D52E118633F}"/>
+    <hyperlink ref="D51" r:id="rId50" display="mailto:lakshmipriya@gmail.com" xr:uid="{A83725F0-0FF6-4B77-A80F-DE572F95F1F3}"/>
+    <hyperlink ref="D52" r:id="rId51" display="mailto:nithya@gmail.com" xr:uid="{A3D793AD-12E9-4AD6-A72D-51A0A212B157}"/>
+    <hyperlink ref="D53" r:id="rId52" display="mailto:sanjana@gmail.com" xr:uid="{3DEA9A78-4C09-4D46-ADF5-6F59F3E8D4E6}"/>
+    <hyperlink ref="D54" r:id="rId53" display="mailto:vaishnavi@gmail.com" xr:uid="{E56E5D1D-10F6-48E2-AF72-59178CA91F05}"/>
+    <hyperlink ref="D55" r:id="rId54" display="mailto:hemalatha@gmail.com" xr:uid="{C726BD77-ED9A-40A5-B004-0970FB0FDF08}"/>
+    <hyperlink ref="D56" r:id="rId55" display="mailto:selvi@gmail.com" xr:uid="{751C491A-9FCD-4738-9600-83DA7E64B62A}"/>
+    <hyperlink ref="D57" r:id="rId56" display="mailto:malathi@gmail.com" xr:uid="{1C93E6D3-C401-402A-B53D-1F32B7D2248C}"/>
+    <hyperlink ref="D58" r:id="rId57" display="mailto:chitra@gmail.com" xr:uid="{AE1EFBD4-CDA9-4E79-82CA-06019F13465E}"/>
+    <hyperlink ref="D59" r:id="rId58" display="mailto:umamaheswari@gmail.com" xr:uid="{F43D2525-3BF5-4346-92FE-12AA629CEA8D}"/>
+    <hyperlink ref="D60" r:id="rId59" display="mailto:bharathkumar@gmail.com" xr:uid="{A9859F1B-192F-48FA-94FD-479353A57679}"/>
+    <hyperlink ref="D61" r:id="rId60" display="mailto:naveena@gmail.com" xr:uid="{3FB39B51-DBC6-4D28-AA17-BA8A7E48FE69}"/>
+    <hyperlink ref="D62" r:id="rId61" display="mailto:rithika@gmail.com" xr:uid="{6F347DA5-955E-4123-95F3-3B8851E9F8A3}"/>
+    <hyperlink ref="D63" r:id="rId62" display="mailto:abinaya@gmail.com" xr:uid="{FD5CE39C-69C6-4364-A0CE-E233F531B749}"/>
+    <hyperlink ref="D64" r:id="rId63" display="mailto:gowtham@gmail.com" xr:uid="{2D8C35F9-E1CB-44F2-9606-E4E75129B4B1}"/>
+    <hyperlink ref="D65" r:id="rId64" display="mailto:arunprasad@gmail.com" xr:uid="{BD743DF5-C37D-4650-B344-B600E82B41D6}"/>
+    <hyperlink ref="D66" r:id="rId65" display="mailto:maheshkumar@gmail.com" xr:uid="{3120E2D9-FED1-4C85-A197-56984E24E938}"/>
+    <hyperlink ref="D67" r:id="rId66" display="mailto:rajeshkumar@gmail.com" xr:uid="{79A6109D-B720-4FC9-BB27-E8B881A2B597}"/>
+    <hyperlink ref="D68" r:id="rId67" display="mailto:kamesh@gmail.com" xr:uid="{CB48D24D-E237-4E94-8F9D-23B1F4D80348}"/>
+    <hyperlink ref="D69" r:id="rId68" display="mailto:yogesh@gmail.com" xr:uid="{81C35A21-03DA-4CB5-A430-83ECA5648333}"/>
+    <hyperlink ref="D70" r:id="rId69" display="mailto:santhoshkumar@gmail.com" xr:uid="{4957098F-C270-44E5-8030-7344AA552C8C}"/>
+    <hyperlink ref="D71" r:id="rId70" display="mailto:vasanth@gmail.com" xr:uid="{9689123A-DFF3-44E5-80C8-A4651E839987}"/>
+    <hyperlink ref="D72" r:id="rId71" display="mailto:murali@gmail.com" xr:uid="{5CF7B1FD-EF90-400B-8C94-ADCEC2B11484}"/>
+    <hyperlink ref="D73" r:id="rId72" display="mailto:parthiban@gmail.com" xr:uid="{F4F28E89-5EFB-4369-84B4-9982C6935B73}"/>
+    <hyperlink ref="D74" r:id="rId73" display="mailto:selvaraj@gmail.com" xr:uid="{A80AFDDB-AE1E-497F-BCD9-22D380D9CE4B}"/>
+    <hyperlink ref="D75" r:id="rId74" display="mailto:kumaravel@gmail.com" xr:uid="{6DAE3499-11BB-4620-AAA4-833C85B55B82}"/>
+    <hyperlink ref="D76" r:id="rId75" display="mailto:boopathy@gmail.com" xr:uid="{74C74642-54DC-42AD-9BB1-FA1B43D70A8F}"/>
+    <hyperlink ref="D77" r:id="rId76" display="mailto:thirumal@gmail.com" xr:uid="{B6B9A52F-F8BA-4C58-823E-453428F68D15}"/>
+    <hyperlink ref="D78" r:id="rId77" display="mailto:ilango@gmail.com" xr:uid="{8A3DF50F-4D20-47EA-A0C9-9B624E2E8BA6}"/>
+    <hyperlink ref="D79" r:id="rId78" display="mailto:perumal@gmail.com" xr:uid="{34ED624F-240B-42A8-9F73-BE56929FE4CA}"/>
+    <hyperlink ref="D80" r:id="rId79" display="mailto:malar@gmail.com" xr:uid="{95550360-0FDF-4265-B93B-304E67EC85E0}"/>
+    <hyperlink ref="D81" r:id="rId80" display="mailto:kanimozhi@gmail.com" xr:uid="{498C34F3-6BBC-4503-9188-3FFC8BFA4B7D}"/>
+    <hyperlink ref="D82" r:id="rId81" display="mailto:thenmozhi@gmail.com" xr:uid="{D0029955-563E-4876-9951-5FC32A044282}"/>
+    <hyperlink ref="D83" r:id="rId82" display="mailto:anbarasi@gmail.com" xr:uid="{B59582A9-C347-4820-A362-114296BCBCE5}"/>
+    <hyperlink ref="D84" r:id="rId83" display="mailto:poornima@gmail.com" xr:uid="{248DFAC6-F35B-4806-A757-A33EF05FF5D3}"/>
+    <hyperlink ref="D85" r:id="rId84" display="mailto:suganya@gmail.com" xr:uid="{0BB5B6E6-2855-49D0-9788-9F62C5E9DF2E}"/>
+    <hyperlink ref="D86" r:id="rId85" display="mailto:rohini@gmail.com" xr:uid="{B95119B9-8243-4FA5-AA60-CFB1DA34D438}"/>
+    <hyperlink ref="D87" r:id="rId86" display="mailto:sangeetha@gmail.com" xr:uid="{B5A2B8EB-25E8-4AEF-B535-29D50409346E}"/>
+    <hyperlink ref="D88" r:id="rId87" display="mailto:bhavani@gmail.com" xr:uid="{B933B64E-5A92-482E-A01B-4FEB09544F64}"/>
+    <hyperlink ref="D89" r:id="rId88" display="mailto:kokila@gmail.com" xr:uid="{4ED53F70-AE17-4902-A0F4-88797D99C5DF}"/>
+    <hyperlink ref="D90" r:id="rId89" display="mailto:sridevi@gmail.com" xr:uid="{D48651A8-CF01-403A-979B-B4F66692E009}"/>
+    <hyperlink ref="D91" r:id="rId90" display="mailto:vidhya@gmail.com" xr:uid="{0577CF7C-A955-4472-83EC-277CC26544EA}"/>
+    <hyperlink ref="D92" r:id="rId91" display="mailto:elango@gmail.com" xr:uid="{2F70A94C-8EDD-4210-9C20-CD1BAD891768}"/>
+    <hyperlink ref="D93" r:id="rId92" display="mailto:chandru@gmail.com" xr:uid="{6C272207-254B-4CB7-B867-A4A37FDDCFB5}"/>
+    <hyperlink ref="D94" r:id="rId93" display="mailto:prithvi@gmail.com" xr:uid="{6101FF68-0A71-4F4F-B62E-7884CE25B49E}"/>
+    <hyperlink ref="D95" r:id="rId94" display="mailto:devan@gmail.com" xr:uid="{4E23B004-06D7-4604-9E6F-7E5A658AF5C2}"/>
+    <hyperlink ref="D96" r:id="rId95" display="mailto:kowsalya@gmail.com" xr:uid="{7F0CA384-0CB3-484E-ACA9-7092E94E5DAA}"/>
+    <hyperlink ref="D97" r:id="rId96" display="mailto:renuka@gmail.com" xr:uid="{B5121CD3-56FF-4091-AE3B-C8A2D4B5324A}"/>
+    <hyperlink ref="D98" r:id="rId97" display="mailto:madhumitha@gmail.com" xr:uid="{0427B80F-EB9D-47A3-9298-D46C8D9DAE6F}"/>
+    <hyperlink ref="D99" r:id="rId98" display="mailto:jothika@gmail.com" xr:uid="{6C51BE3E-DB8F-48FE-9D0C-5FEC085EB456}"/>
+    <hyperlink ref="D100" r:id="rId99" display="mailto:thamarai@gmail.com" xr:uid="{B642DC14-C65E-4E03-B531-ADC668A2DE34}"/>
+    <hyperlink ref="D101" r:id="rId100" display="mailto:iniyan@gmail.com" xr:uid="{AFC574C4-2D58-4F27-96F4-12B0290E8E21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6229,4 +10607,1041 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C978212-B2AD-40F0-B7B8-EB72EA4E74DF}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="77.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>709</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18">
+        <v>3</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18">
+        <v>4</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18">
+        <v>5</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18">
+        <v>6</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18">
+        <v>7</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18">
+        <v>8</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18">
+        <v>9</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18">
+        <v>10</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>727</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18">
+        <v>11</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18">
+        <v>12</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>718</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18">
+        <v>13</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18">
+        <v>14</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
+        <v>15</v>
+      </c>
+      <c r="B16" s="18">
+        <v>15</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18">
+        <v>16</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18">
+        <v>17</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18">
+        <v>18</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>19</v>
+      </c>
+      <c r="B20" s="18">
+        <v>19</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18">
+        <v>20</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18">
+        <v>21</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="18">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18">
+        <v>22</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18">
+        <v>23</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="18">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18">
+        <v>24</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <v>25</v>
+      </c>
+      <c r="B26" s="18">
+        <v>25</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18">
+        <v>26</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18">
+        <v>27</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18">
+        <v>28</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="18">
+        <v>29</v>
+      </c>
+      <c r="B30" s="18">
+        <v>29</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="18">
+        <v>30</v>
+      </c>
+      <c r="B31" s="18">
+        <v>30</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <v>31</v>
+      </c>
+      <c r="B32" s="18">
+        <v>31</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E32" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
+        <v>32</v>
+      </c>
+      <c r="B33" s="18">
+        <v>32</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <v>33</v>
+      </c>
+      <c r="B34" s="18">
+        <v>33</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="18">
+        <v>34</v>
+      </c>
+      <c r="B35" s="18">
+        <v>34</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="18">
+        <v>35</v>
+      </c>
+      <c r="B36" s="18">
+        <v>35</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="18">
+        <v>36</v>
+      </c>
+      <c r="B37" s="18">
+        <v>36</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="18">
+        <v>37</v>
+      </c>
+      <c r="B38" s="18">
+        <v>37</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="18">
+        <v>38</v>
+      </c>
+      <c r="B39" s="18">
+        <v>38</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="18">
+        <v>39</v>
+      </c>
+      <c r="B40" s="18">
+        <v>39</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>727</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="18">
+        <v>40</v>
+      </c>
+      <c r="B41" s="18">
+        <v>40</v>
+      </c>
+      <c r="C41" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="18">
+        <v>41</v>
+      </c>
+      <c r="B42" s="18">
+        <v>41</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="18">
+        <v>42</v>
+      </c>
+      <c r="B43" s="18">
+        <v>42</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="18">
+        <v>43</v>
+      </c>
+      <c r="B44" s="18">
+        <v>43</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="18">
+        <v>44</v>
+      </c>
+      <c r="B45" s="18">
+        <v>44</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>717</v>
+      </c>
+      <c r="E45" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F45" s="18" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="18">
+        <v>45</v>
+      </c>
+      <c r="B46" s="18">
+        <v>45</v>
+      </c>
+      <c r="C46" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F46" s="18" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="18">
+        <v>46</v>
+      </c>
+      <c r="B47" s="18">
+        <v>46</v>
+      </c>
+      <c r="C47" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E47" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F47" s="18" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="18">
+        <v>47</v>
+      </c>
+      <c r="B48" s="18">
+        <v>47</v>
+      </c>
+      <c r="C48" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F48" s="18" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="18">
+        <v>48</v>
+      </c>
+      <c r="B49" s="18">
+        <v>48</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="18">
+        <v>49</v>
+      </c>
+      <c r="B50" s="18">
+        <v>49</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>712</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="18">
+        <v>50</v>
+      </c>
+      <c r="B51" s="18">
+        <v>50</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>715</v>
+      </c>
+      <c r="E51" s="18" t="s">
+        <v>713</v>
+      </c>
+      <c r="F51" s="18" t="s">
+        <v>768</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>